--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -849,6 +849,68 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>01. History_Transposed</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>01 History_T</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Incurred Losses</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Year basis</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Premium basis</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Loss basis</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>PF transfer</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>As at</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +140,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1142,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1396,50 +1397,76 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>2025 9 months</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>7100</v>
+      </c>
+      <c r="L14" s="17">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C14" s="18">
-        <f>SUM(C9:C13)</f>
-        <v>6910</v>
-      </c>
-      <c r="D14" s="18">
-        <f>SUM(D9:D13)</f>
-        <v>87750</v>
-      </c>
-      <c r="G14" s="18">
-        <f>SUM(G9:G13)</f>
-        <v>59570</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="C15" s="19">
+        <f>SUM(C9:C14)</f>
+        <v>8090</v>
+      </c>
+      <c r="D15" s="19">
+        <f>SUM(D9:D14)</f>
+        <v>102150</v>
+      </c>
+      <c r="G15" s="19">
+        <f>SUM(G9:G14)</f>
+        <v>66670</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>← selector empty: excluded from extraction, reused as control</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Note: 2025 figures preliminary</t>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Note: 2025 shown both as a full year and as the first nine months</t>
         </is>
       </c>
     </row>
@@ -1454,18 +1481,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1548,7 +1576,12 @@
       <c r="H8" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>2025 9 months</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -1575,9 +1608,12 @@
       <c r="H9" s="14" t="n">
         <v>1505</v>
       </c>
-      <c r="I9" s="18">
-        <f>SUM(D9:H9)</f>
-        <v>6910</v>
+      <c r="I9" s="14" t="n">
+        <v>1180</v>
+      </c>
+      <c r="J9" s="19">
+        <f>SUM(D9:I9)</f>
+        <v>8090</v>
       </c>
     </row>
     <row r="10">
@@ -1611,9 +1647,12 @@
       <c r="H10" s="14" t="n">
         <v>19200</v>
       </c>
-      <c r="I10" s="18">
-        <f>SUM(D10:H10)</f>
-        <v>87750</v>
+      <c r="I10" s="14" t="n">
+        <v>14400</v>
+      </c>
+      <c r="J10" s="19">
+        <f>SUM(D10:I10)</f>
+        <v>102150</v>
       </c>
     </row>
     <row r="11">
@@ -1637,6 +1676,9 @@
       <c r="H11" s="15" t="n">
         <v>0.235</v>
       </c>
+      <c r="I11" s="15" t="n">
+        <v>0.235</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
@@ -1659,6 +1701,9 @@
       <c r="H12" s="16" t="n">
         <v>1.05</v>
       </c>
+      <c r="I12" s="16" t="n">
+        <v>1.05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1691,9 +1736,12 @@
       <c r="H13" s="14" t="n">
         <v>10250</v>
       </c>
-      <c r="I13" s="18">
-        <f>SUM(D13:H13)</f>
-        <v>59570</v>
+      <c r="I13" s="14" t="n">
+        <v>7100</v>
+      </c>
+      <c r="J13" s="19">
+        <f>SUM(D13:I13)</f>
+        <v>66670</v>
       </c>
     </row>
     <row r="16">
@@ -1727,6 +1775,10 @@
         <f>COLUMN()</f>
         <v>8</v>
       </c>
+      <c r="I16" s="17">
+        <f>COLUMN()</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -1738,7 +1790,7 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Column I (Total) has no selector: excluded from extraction, reused as control.</t>
+          <t>The Total column has no selector: excluded from extraction, reused as control.</t>
         </is>
       </c>
     </row>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -10,6 +10,7 @@
     <sheet name="00. NC+Interdep" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="01. History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="01. History_Transposed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="02. EPI Projections" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +55,10 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -121,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,9 +136,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,6 +149,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,12 +515,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T34"/>
+  <dimension ref="B1:T61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -542,14 +550,14 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Dictionary of names for humans. Column A is intentionally empty — no markers in this sheet.</t>
+          <t>The frame: what each sheet holds, what the names mean, what must tie. Column A is intentionally empty — no markers in this sheet.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Row 5 (dataset 01) is agreed. Rows 6-9 are provisional sketches, not yet specified.</t>
+          <t>Rows 7-9 are provisional sketches, not yet specified.</t>
         </is>
       </c>
     </row>
@@ -638,42 +646,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>02. EPI Projections</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>02 EPI</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>Premium basis</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -912,221 +925,574 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Note: 'Year' is deliberately unqualified — underwriting vs occurrence is an attribute, not part of the field name.</t>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>⟦GLOBAL⟧</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>⟦VOCABULARY⟧</t>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Permitted values</t>
-        </is>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Actual year</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Example Insurance SA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
+          <t>Treaty</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Property per Risk XL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>PF transfer</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>with clean cut | without clean cut | none</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Exposure basis</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Incurred Losses</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>EPI</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Claim Reference</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Loss Date</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>⟦VOCABULARY⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Permitted values</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Year basis</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>UW | Occurrence</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Premium basis</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Loss basis</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Paid | Incurred</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>PF transfer</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>with clean cut | without clean cut | none</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured | EML | PML | MPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of each data sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="8" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>⟦RULES⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>01 History.Premium@{N} 9 months</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} 9 months</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>same nine months reported in two sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>01 History.Premium@{N}</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} re-est</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>a full-year N in History is an estimate, not an actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} re-est</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} 9 months</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Form: &lt;key&gt;.&lt;field&gt;@&lt;record&gt;.  {N} resolves from ⟦GLOBAL⟧; records match on leading number, then suffix. A rule is skipped, not guessed, when Premium basis / Currency differ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="9" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="9" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>block i is transposed</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="9" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>an attribute of the sheet (unsuffixed) or of block i (suffixed _i)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="9" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>the same, declared as a hypothesis — auto-registers a query</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="8" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>the same, declared as a hypothesis — raises a query</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -1147,16 +1513,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="4" customWidth="1" min="9" max="9"/>
-    <col width="4" customWidth="1" min="10" max="10"/>
-    <col width="4" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -1168,7 +1531,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
@@ -1180,28 +1543,28 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
@@ -1250,22 +1613,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -1277,153 +1640,153 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="15" t="n">
         <v>2021</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="16" t="n">
         <v>1240</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="16" t="n">
         <v>15900</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="17" t="n">
         <v>0.225</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="18" t="n">
         <v>1.02</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="16" t="n">
         <v>14930</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="19">
         <f>ROW()</f>
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="15" t="n">
         <v>2022</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="16" t="n">
         <v>1310</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="16" t="n">
         <v>16740</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="17" t="n">
         <v>0.225</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="18" t="n">
         <v>1.04</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="16" t="n">
         <v>10030</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="19">
         <f>ROW()</f>
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="15" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="16" t="n">
         <v>1395</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="16" t="n">
         <v>17520</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="17" t="n">
         <v>0.23</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="18" t="n">
         <v>1.06</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="16" t="n">
         <v>12660</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="19">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="15" t="n">
         <v>2024</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="16" t="n">
         <v>1460</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="16" t="n">
         <v>18390</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="17" t="n">
         <v>0.23</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="18" t="n">
         <v>1.03</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="16" t="n">
         <v>11700</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="15" t="n">
         <v>2025</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="16" t="n">
         <v>1505</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="16" t="n">
         <v>19200</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="17" t="n">
         <v>0.235</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="18" t="n">
         <v>1.05</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="16" t="n">
         <v>10250</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="16" t="n">
         <v>1180</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="16" t="n">
         <v>14400</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="17" t="n">
         <v>0.235</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="18" t="n">
         <v>1.05</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="16" t="n">
         <v>7100</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -1433,15 +1796,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="21">
         <f>SUM(C9:C14)</f>
         <v>8090</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="21">
         <f>SUM(D9:D14)</f>
         <v>102150</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="21">
         <f>SUM(G9:G14)</f>
         <v>66670</v>
       </c>
@@ -1452,14 +1815,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -1504,49 +1867,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Transpose_1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Header_1 = C</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Info_1 = 16</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -1556,27 +1919,27 @@
           <t>UW Year</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="15" t="n">
         <v>2021</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="15" t="n">
         <v>2022</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="15" t="n">
         <v>2023</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="15" t="n">
         <v>2024</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="15" t="n">
         <v>2025</v>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
@@ -1593,31 +1956,31 @@
           <t>Policies</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="16" t="n">
         <v>1240</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="16" t="n">
         <v>1310</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="16" t="n">
         <v>1395</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="16" t="n">
         <v>1460</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="16" t="n">
         <v>1505</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="16" t="n">
         <v>1180</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="21">
         <f>SUM(D9:I9)</f>
         <v>8090</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
@@ -1627,30 +1990,30 @@
           <t>Prem.</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="16" t="n">
         <v>15900</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="16" t="n">
         <v>16740</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="16" t="n">
         <v>17520</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="16" t="n">
         <v>18390</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="16" t="n">
         <v>19200</v>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="16" t="n">
         <v>14400</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="21">
         <f>SUM(D10:I10)</f>
         <v>102150</v>
       </c>
@@ -1661,22 +2024,22 @@
           <t>Comm. %</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="17" t="n">
         <v>0.225</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="17" t="n">
         <v>0.225</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="17" t="n">
         <v>0.23</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="17" t="n">
         <v>0.23</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="17" t="n">
         <v>0.235</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="17" t="n">
         <v>0.235</v>
       </c>
     </row>
@@ -1686,27 +2049,27 @@
           <t>Rate</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="18" t="n">
         <v>1.02</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="18" t="n">
         <v>1.04</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="18" t="n">
         <v>1.06</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="18" t="n">
         <v>1.03</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="18" t="n">
         <v>1.05</v>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="18" t="n">
         <v>1.05</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -1716,36 +2079,36 @@
           <t>Incurred</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="16" t="n">
         <v>14930</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="16" t="n">
         <v>10030</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="16" t="n">
         <v>12660</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="16" t="n">
         <v>11700</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="16" t="n">
         <v>10250</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="16" t="n">
         <v>7100</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="21">
         <f>SUM(D13:I13)</f>
         <v>66670</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -1755,27 +2118,27 @@
           <t>selector →</t>
         </is>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="19">
         <f>COLUMN()</f>
         <v>4</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="19">
         <f>COLUMN()</f>
         <v>5</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="19">
         <f>COLUMN()</f>
         <v>6</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="19">
         <f>COLUMN()</f>
         <v>7</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="19">
         <f>COLUMN()</f>
         <v>8</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="19">
         <f>COLUMN()</f>
         <v>9</v>
       </c>
@@ -1791,6 +2154,254 @@
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>The Total column has no selector: excluded from extraction, reused as control.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>02. EPI Projections — premium projections for N and N+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Currency = USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Scale = 1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Premium basis = GNPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>H_Year basis = UW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Treaty XYZ — Property per Risk XL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>EPI (net)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Share %</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>selector</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>EPI</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: Share % and Comment are not declared in 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>2025 est</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>18500</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>as advised at last renewal</t>
+        </is>
+      </c>
+      <c r="K9" s="19">
+        <f>ROW()</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>2025 9 months</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>14400</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>booked to 30.09</t>
+        </is>
+      </c>
+      <c r="K10" s="19">
+        <f>ROW()</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>2025 re-est</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>19200</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>current view</t>
+        </is>
+      </c>
+      <c r="K11" s="19">
+        <f>ROW()</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>20900</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>renewal projection</t>
+        </is>
+      </c>
+      <c r="K12" s="19">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>2024 actual</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>17800</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>covered by 01. History</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: not extracted here</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Info_1 = K</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>As at = 31.12.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No total row: est, 9 months and re-est are three views of one year, so a sum of them would mean nothing.</t>
         </is>
       </c>
     </row>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -11,6 +11,7 @@
     <sheet name="01. History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="01. History_Transposed" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="02. EPI Projections" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="02. EPI Projections_Transposed" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,12 +138,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -515,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T61"/>
+  <dimension ref="B1:T74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -925,142 +926,160 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>02. EPI Projections_Transposed</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>02 EPI_T</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>EPI</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Year basis</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Premium basis</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>As at</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>⟦GLOBAL⟧</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="8" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Actual year</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>2025</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Cedent</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Example Insurance SA</t>
-        </is>
+          <t>Actual year</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Example Insurance SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>Treaty</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Property per Risk XL</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Actual year is N: the expiring year. The renewal being underwritten is N+1. Sheet attributes override these; block attributes override the sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Incurred Losses</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Number of Risks</t>
+          <t>Incurred Losses</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1072,7 +1091,7 @@
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1084,7 +1103,7 @@
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1096,403 +1115,502 @@
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Loss Date</t>
+          <t>Sum Insured</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>Claim Reference</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Loss Date</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>A field name carries one type across the whole workbook. Year is text because 2026 and '2026 9 months' are two records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="8" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>PF transfer</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>with clean cut | without clean cut | none</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Exposure basis</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
+          <t>Premium basis</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Loss basis</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Paid | Incurred</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>PF transfer</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>with clean cut | without clean cut | none</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured | EML | PML | MPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>⟦PERIOD ORDER⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>re-est</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Within one year the suffixes sort in this order, not alphabetically: est comes before 9 months even though '9' &lt; 'e'. A bare year sorts first; an unlisted suffix sorts last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="8" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="8" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>01 History.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F58" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="8" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>01 History.Premium@{N}</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E59" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F59" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="8" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E60" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="2" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Form: &lt;key&gt;.&lt;field&gt;@&lt;record&gt;.  {N} resolves from ⟦GLOBAL⟧; records match on leading number, then suffix. A rule is skipped, not guessed, when Premium basis / Currency differ.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="8" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="11" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="11" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="11" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="11" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="11" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>block i is transposed</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="11" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="11" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="8" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -1531,7 +1649,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
@@ -1543,28 +1661,28 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
@@ -1613,22 +1731,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -1640,7 +1758,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="10" t="n">
         <v>2021</v>
       </c>
       <c r="C9" s="16" t="n">
@@ -1664,7 +1782,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="10" t="n">
         <v>2022</v>
       </c>
       <c r="C10" s="16" t="n">
@@ -1688,7 +1806,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="10" t="n">
         <v>2023</v>
       </c>
       <c r="C11" s="16" t="n">
@@ -1712,7 +1830,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="10" t="n">
         <v>2024</v>
       </c>
       <c r="C12" s="16" t="n">
@@ -1736,7 +1854,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="10" t="n">
         <v>2025</v>
       </c>
       <c r="C13" s="16" t="n">
@@ -1786,7 +1904,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -1815,14 +1933,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -1867,49 +1985,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Transpose_1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Header_1 = C</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Info_1 = 16</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -1919,24 +2037,24 @@
           <t>UW Year</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="10" t="n">
         <v>2021</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="10" t="n">
         <v>2022</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="10" t="n">
         <v>2023</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="10" t="n">
         <v>2024</v>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="H8" s="10" t="n">
         <v>2025</v>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1980,7 +2098,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
@@ -1990,7 +2108,7 @@
           <t>Prem.</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
@@ -2069,7 +2187,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -2079,7 +2197,7 @@
           <t>Incurred</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2108,7 +2226,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2188,28 +2306,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
@@ -2255,17 +2373,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -2385,14 +2503,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2402,6 +2520,237 @@
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>No total row: est, 9 months and re-est are three views of one year, so a sum of them would mean nothing.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>02. EPI Projections — transposed (same data, same result)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Currency = USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Scale = 1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Premium basis = GNPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Transpose_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Header_1 = C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Info_1 = 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>H_Year basis = UW</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>2025 est</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>2025 9 months</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>2025 re-est</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>2024 actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Share %</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>As at = 31.12.2025</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>EPI (net)</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>EPI</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>18500</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>14400</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>19200</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>20900</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>17800</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>as advised at last renewal</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>booked to 30.09</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>current view</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>renewal projection</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>covered by 01. History</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>selector →</t>
+        </is>
+      </c>
+      <c r="D14" s="19">
+        <f>COLUMN()</f>
+        <v>4</v>
+      </c>
+      <c r="E14" s="19">
+        <f>COLUMN()</f>
+        <v>5</v>
+      </c>
+      <c r="F14" s="19">
+        <f>COLUMN()</f>
+        <v>6</v>
+      </c>
+      <c r="G14" s="19">
+        <f>COLUMN()</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Column H (2024 actual) has no selector: not extracted here, because 01. History carries the actuals.</t>
         </is>
       </c>
     </row>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -12,6 +12,7 @@
     <sheet name="01. History_Transposed" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="02. EPI Projections" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="02. EPI Projections_Transposed" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="03. Large Losses" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -127,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -151,6 +153,7 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T74"/>
+  <dimension ref="B1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -558,7 +561,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Rows 7-9 are provisional sketches, not yet specified.</t>
+          <t>Rows 8-9 are provisional sketches, not yet specified.</t>
         </is>
       </c>
     </row>
@@ -622,25 +625,30 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="S5" s="6" t="inlineStr">
         <is>
           <t>Loss basis</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="T5" s="6" t="inlineStr">
         <is>
           <t>PF transfer</t>
         </is>
       </c>
-      <c r="T5" s="6" t="inlineStr">
+      <c r="U5" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -679,77 +687,92 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="S6" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>03. Large Losses</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>03 Large</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Loss Date</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Claim Reference</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Incurred Losses</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Name of Loss</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Loss amount</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>Loss basis</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="S7" s="6" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -902,25 +925,30 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="S10" s="6" t="inlineStr">
         <is>
           <t>Loss basis</t>
         </is>
       </c>
-      <c r="S10" s="6" t="inlineStr">
+      <c r="T10" s="6" t="inlineStr">
         <is>
           <t>PF transfer</t>
         </is>
       </c>
-      <c r="T10" s="6" t="inlineStr">
+      <c r="U10" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -959,15 +987,20 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1005,81 +1038,81 @@
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Cedent</t>
+          <t>Treaty type</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Example Insurance SA</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Example Insurance SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>Treaty</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Property per Risk XL</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Actual year is N: the expiring year. The renewal being underwritten is N+1. Sheet attributes override these; block attributes override the sheet.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Incurred Losses</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1091,7 +1124,7 @@
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>Incurred Losses</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1103,31 +1136,31 @@
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Number of Risks</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1139,19 +1172,19 @@
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Sum Insured</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Claim Reference</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1163,7 +1196,7 @@
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Loss Date</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1175,442 +1208,572 @@
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>Name of Loss</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Loss amount</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook. Year is text because 2026 and '2026 9 months' are two records.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="3" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="8" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
+          <t>PF transfer</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>with clean cut | without clean cut | none</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured | EML | PML | MPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="3" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="8" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="10" t="n">
+    <row r="55">
+      <c r="B55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="10" t="n">
+    <row r="56">
+      <c r="B56" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="10" t="n">
+    <row r="57">
+      <c r="B57" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="2" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically: est comes before 9 months even though '9' &lt; 'e'. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="3" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="8" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="8" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>01 History.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F63" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="8" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C59" s="11" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>01 History.Premium@{N}</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr">
+      <c r="E64" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F64" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>a full-year N in History is an estimate, not an actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>R-07</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Form: &lt;key&gt;.&lt;field&gt;@&lt;record&gt;.  {N} resolves from ⟦GLOBAL⟧; records match on leading number, then suffix. A rule is skipped, not guessed, when Premium basis / Currency differ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="8" t="inlineStr">
         <is>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} re-est</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} 9 months</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>SUM(03 Large.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>large losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>01 History.Year basis</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>03 Large.Year basis</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="8" t="inlineStr">
+        <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="12" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="12" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="12" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="12" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="12" t="inlineStr">
+    <row r="77">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>block i is transposed</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="12" t="inlineStr">
+    <row r="78">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="12" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="8" t="inlineStr">
+    <row r="81">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -1689,6 +1852,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
           <t>UW Year</t>
@@ -2069,6 +2237,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Policies</t>
@@ -2334,9 +2507,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Treaty XYZ — Property per Risk XL</t>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
@@ -2639,6 +2812,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Share %</t>
@@ -2751,6 +2929,403 @@
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Column H (2024 actual) has no selector: not extracted here, because 01. History carries the actuals.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>03. Large Losses — individual claims above the threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Currency = USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Scale = 1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>H_Year basis = UW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>H_Loss basis = Incurred</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Threshold = 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Date format = ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Claim no.</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>U/W Yr</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Gross incurred</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Occurred</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Name of Loss</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Loss amount</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: the claim number is not declared in 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>CL-2100</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Warehouse fire, Lyon</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>44269</v>
+      </c>
+      <c r="J11" s="19">
+        <f>ROW()</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CL-2101</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Machinery breakdown, Hamburg</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>920</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>44441</v>
+      </c>
+      <c r="J12" s="19">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>CL-2102</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Factory fire, Rotterdam</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>3400</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>44953</v>
+      </c>
+      <c r="J13" s="19">
+        <f>ROW()</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>CL-2103</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Explosion, Antwerp</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>45092</v>
+      </c>
+      <c r="J14" s="19">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>CL-2104</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Storm damage, Bremen</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>780</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>45238</v>
+      </c>
+      <c r="J15" s="19">
+        <f>ROW()</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>CL-2105</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Chemical plant fire, Basel</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>45431</v>
+      </c>
+      <c r="J16" s="19">
+        <f>ROW()</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>CL-2106</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Cold store collapse, Milan</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>45699</v>
+      </c>
+      <c r="J17" s="19">
+        <f>ROW()</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>CL-2107</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Transformer fire, Porto</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>640</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>45892</v>
+      </c>
+      <c r="J18" s="19">
+        <f>ROW()</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E19" s="21">
+        <f>SUM(E11:E18)</f>
+        <v>12760</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Info_1 = J</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>As at = 31.12.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2022 has no large loss. The annual table in step 2 shows it as 0, because an absent year reads as 'no data' rather than 'nothing happened'.</t>
         </is>
       </c>
     </row>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:U81"/>
+  <dimension ref="B1:V88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -615,40 +615,45 @@
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="S5" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="T5" s="6" t="inlineStr">
         <is>
           <t>Loss basis</t>
         </is>
       </c>
-      <c r="T5" s="6" t="inlineStr">
+      <c r="U5" s="6" t="inlineStr">
         <is>
           <t>PF transfer</t>
         </is>
       </c>
-      <c r="U5" s="6" t="inlineStr">
+      <c r="V5" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -677,30 +682,35 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="S6" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="S6" s="6" t="inlineStr">
+      <c r="T6" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -739,40 +749,45 @@
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="S7" s="6" t="inlineStr">
         <is>
           <t>Loss basis</t>
         </is>
       </c>
-      <c r="S7" s="6" t="inlineStr">
+      <c r="T7" s="6" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="T7" s="6" t="inlineStr">
+      <c r="U7" s="6" t="inlineStr">
         <is>
           <t>Date format</t>
         </is>
       </c>
-      <c r="U7" s="6" t="inlineStr">
+      <c r="V7" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -915,40 +930,45 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="O10" s="6" t="inlineStr">
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="S10" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="S10" s="6" t="inlineStr">
+      <c r="T10" s="6" t="inlineStr">
         <is>
           <t>Loss basis</t>
         </is>
       </c>
-      <c r="T10" s="6" t="inlineStr">
+      <c r="U10" s="6" t="inlineStr">
         <is>
           <t>PF transfer</t>
         </is>
       </c>
-      <c r="U10" s="6" t="inlineStr">
+      <c r="V10" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -977,30 +997,35 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
+      <c r="T11" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1009,771 +1034,889 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>⟦GLOBAL⟧</t>
+          <t>⟦SECTIONS⟧</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="inlineStr">
         <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Datasets</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>One per-risk section: a Fire treaty. Large losses (03) apply; cat losses (04) do not, so rules scoped 'cat' are not applicable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>⟦GLOBAL⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Actual year</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C21" s="9" t="n">
         <v>2025</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Treaty type</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Fire</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Cedent</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Example Insurance SA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Treaty</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Property per Risk XL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Actual year is N: the expiring year. The renewal being underwritten is N+1. Sheet attributes override these; block attributes override the sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>⟦TYPES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+          <t>Treaty</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Property per Risk XL</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Incurred Losses</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Actual year is N: the expiring year. The renewal being underwritten is N+1. Sheet attributes override these; block attributes override the sheet.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Band</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Number of Risks</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Incurred Losses</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Sum Insured</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Claim Reference</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Name of Loss</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Loss amount</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
           <t>date</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>A field name carries one type across the whole workbook. Year is text because 2026 and '2026 9 months' are two records.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>⟦VOCABULARY⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Permitted values</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>PF transfer</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>with clean cut | without clean cut | none</t>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>A field name carries one type across the whole workbook. Year is text because 2026 and '2026 9 months' are two records.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Exposure basis</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>1 | 1,000 | 1,000,000</t>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Permitted values</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
+          <t>Loss basis</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Paid | Incurred</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>PF transfer</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>with clean cut | without clean cut | none</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured | EML | PML | MPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="3" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="8" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="10" t="n">
+    <row r="61">
+      <c r="B61" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="10" t="n">
+    <row r="62">
+      <c r="B62" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="10" t="n">
+    <row r="63">
+      <c r="B63" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="2" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically: est comes before 9 months even though '9' &lt; 'e'. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="3" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="8" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="8" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>01 History.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr">
+      <c r="E69" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="F69" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="8" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>01 History.Premium@{N}</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="E70" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F70" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="8" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E71" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="F71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>premium accrues; a re-estimate cannot fall below what is booked</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>SUM(03 Large.Loss amount@{Y})</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Incurred Losses@{Y}</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>R-09</t>
-        </is>
-      </c>
-      <c r="C67" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Year basis</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>03 Large.Year basis</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>history and large losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="8" t="inlineStr">
         <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>SUM(03 Large.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>large losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>01 History.Year basis</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>03 Large.Year basis</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>SUM(04 Cat.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="8" t="inlineStr">
+        <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="12" t="inlineStr">
+    <row r="80">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="12" t="inlineStr">
+    <row r="81">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="12" t="inlineStr">
+    <row r="82">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="12" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="12" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>block i is transposed</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="12" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="12" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="8" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -1805,6 +1948,11 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Section = Fire</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. History — row-wise reference block</t>
@@ -2146,6 +2294,11 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Section = Fire</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. History — transposed reference block (same data, same result)</t>
@@ -2472,6 +2625,11 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Section = Fire</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>02. EPI Projections — premium projections for N and N+1</t>
@@ -2721,6 +2879,11 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Section = Fire</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>02. EPI Projections — transposed (same data, same result)</t>
@@ -2957,6 +3120,11 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Section = Fire</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>03. Large Losses — individual claims above the threshold</t>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V88"/>
+  <dimension ref="B1:V93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Rows 8-9 are provisional sketches, not yet specified.</t>
+          <t>Greyed rows are provisional sketches, not yet specified. 04 is specified, though this Fire-only pack carries no cat sheet.</t>
         </is>
       </c>
     </row>
@@ -794,57 +794,92 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>04. Cat Losses</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>04 Cat</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Loss amount</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Incurred Losses</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Number of Claims (optional)</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="P8" s="7" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="S8" s="6" t="inlineStr">
         <is>
           <t>Loss basis</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr">
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="U8" s="6" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1293,447 +1328,335 @@
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
+          <t>Number of Claims</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook. Year is text because 2026 and '2026 9 months' are two records.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="3" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="8" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="3" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="8" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="10" t="n">
+    <row r="65">
+      <c r="B65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="10" t="n">
+    <row r="66">
+      <c r="B66" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="10" t="n">
+    <row r="67">
+      <c r="B67" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="2" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically: est comes before 9 months even though '9' &lt; 'e'. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="3" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Premium@{N}</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>R-07</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>SUM(03 Large.Loss amount@{Y})</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Incurred Losses@{Y}</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>01 History.Year basis</t>
+          <t>01 History.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -1743,11 +1666,11 @@
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>03 Large.Year basis</t>
+          <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
@@ -1756,34 +1679,34 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>SUM(04 Cat.Loss amount@{Y})</t>
+          <t>01 History.Premium@{N}</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>01 History.Incurred Losses@{Y}</t>
+          <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
@@ -1796,127 +1719,327 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>a full-year N in History is an estimate, not an actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} re-est</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} 9 months</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>SUM(03 Large.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>large losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>01 History.Year basis</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>03 Large.Year basis</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>SUM(04 Cat.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>cat losses cannot exceed total incurred for the same year</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
         <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>01 History.Year basis</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>04 Cat.Year basis</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>history and cat losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="8" t="inlineStr">
+        <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="12" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;row&gt;</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>Transpose_i</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="12" t="inlineStr">
         <is>
+          <t>Header_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this column is block i's extraction column</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;row&gt;</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Transpose_i</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>block i is transposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="12" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="8" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +140,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -519,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V93"/>
+  <dimension ref="B1:V94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1179,60 +1180,58 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Actual year is N: the expiring year. The renewal being underwritten is N+1. Sheet attributes override these; block attributes override the sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Loss share warning</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Actual year is N: the expiring year. The renewal being underwritten is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="8" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Incurred Losses</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1244,7 +1243,7 @@
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>Incurred Losses</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1256,31 +1255,31 @@
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Number of Risks</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1292,19 +1291,19 @@
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Sum Insured</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Claim Reference</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1316,7 +1315,7 @@
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1328,7 +1327,7 @@
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
+          <t>Name of Loss</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1340,19 +1339,19 @@
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Number of Claims</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1364,19 +1363,19 @@
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Number of Claims</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Date of Loss</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1388,315 +1387,287 @@
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook. Year is text because 2026 and '2026 9 months' are two records.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="3" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="8" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Premium basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Paid | Incurred</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Date format</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="3" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="8" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="10" t="n">
+    <row r="66">
+      <c r="B66" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="10" t="n">
+    <row r="67">
+      <c r="B67" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="10" t="n">
+    <row r="68">
+      <c r="B68" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically: est comes before 9 months even though '9' &lt; 'e'. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="3" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Premium@{N} 9 months</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Premium@{N}</t>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -1704,9 +1675,9 @@
           <t>=</t>
         </is>
       </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} re-est</t>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
@@ -1724,33 +1695,33 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Premium@{N}</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} 9 months</t>
-        </is>
-      </c>
       <c r="F75" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
@@ -1764,33 +1735,33 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>SUM(03 Large.Loss amount@{Y})</t>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Incurred Losses@{Y}</t>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
@@ -1799,38 +1770,38 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Year basis</t>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>SUM(03 Large.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>03 Large.Year basis</t>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
@@ -1844,33 +1815,33 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>SUM(04 Cat.Loss amount@{Y})</t>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Year basis</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Incurred Losses@{Y}</t>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>03 Large.Year basis</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -1879,167 +1850,207 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>per risk</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>history and large losses must be on the same year basis</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
         <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04 Cat.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="8" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C79" s="11" t="inlineStr">
+      <c r="C80" s="12" t="inlineStr">
         <is>
           <t>01 History.Year basis</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E79" s="11" t="inlineStr">
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t>04 Cat.Year basis</t>
         </is>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F80" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="3" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="8" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="12" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="12" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="13" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="12" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="12" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="13" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="12" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>block i is transposed</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="12" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="12" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="8" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2071,7 +2082,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -2083,7 +2094,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
@@ -2095,35 +2106,35 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
@@ -2170,22 +2181,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2197,153 +2208,153 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>1240</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>15900</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.225</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>1.02</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>14930</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="20">
         <f>ROW()</f>
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>1310</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>16740</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.225</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>1.04</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="17" t="n">
         <v>10030</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="20">
         <f>ROW()</f>
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>1395</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>17520</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.23</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>1.06</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="17" t="n">
         <v>12660</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>1460</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>18390</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.23</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>1.03</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>11700</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>1505</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>19200</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.235</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>1.05</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>10250</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>1180</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>14400</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>0.235</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>1.05</v>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <v>7100</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -2353,15 +2364,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <f>SUM(C9:C14)</f>
         <v>8090</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="22">
         <f>SUM(D9:D14)</f>
         <v>102150</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="22">
         <f>SUM(G9:G14)</f>
         <v>66670</v>
       </c>
@@ -2372,14 +2383,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2417,7 +2428,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -2429,49 +2440,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Transpose_1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Header_1 = C</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Info_1 = 16</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -2481,27 +2492,27 @@
           <t>UW Year</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
@@ -2513,7 +2524,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
@@ -2523,31 +2534,31 @@
           <t>Policies</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>1240</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>1310</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>1395</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>1460</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="17" t="n">
         <v>1505</v>
       </c>
-      <c r="I9" s="16" t="n">
+      <c r="I9" s="17" t="n">
         <v>1180</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="22">
         <f>SUM(D9:I9)</f>
         <v>8090</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
@@ -2557,30 +2568,30 @@
           <t>Prem.</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>15900</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>16740</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>17520</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="17" t="n">
         <v>18390</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="17" t="n">
         <v>19200</v>
       </c>
-      <c r="I10" s="16" t="n">
+      <c r="I10" s="17" t="n">
         <v>14400</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="22">
         <f>SUM(D10:I10)</f>
         <v>102150</v>
       </c>
@@ -2591,22 +2602,22 @@
           <t>Comm. %</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.225</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.225</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.23</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <v>0.23</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="18" t="n">
         <v>0.235</v>
       </c>
-      <c r="I11" s="17" t="n">
+      <c r="I11" s="18" t="n">
         <v>0.235</v>
       </c>
     </row>
@@ -2616,27 +2627,27 @@
           <t>Rate</t>
         </is>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>1.02</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>1.04</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>1.06</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>1.03</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <v>1.05</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="19" t="n">
         <v>1.05</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -2646,36 +2657,36 @@
           <t>Incurred</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>14930</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>10030</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>12660</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>11700</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="17" t="n">
         <v>10250</v>
       </c>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="17" t="n">
         <v>7100</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="22">
         <f>SUM(D13:I13)</f>
         <v>66670</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2685,27 +2696,27 @@
           <t>selector →</t>
         </is>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>COLUMN()</f>
         <v>4</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>COLUMN()</f>
         <v>5</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <f>COLUMN()</f>
         <v>6</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="20">
         <f>COLUMN()</f>
         <v>7</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="20">
         <f>COLUMN()</f>
         <v>8</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>COLUMN()</f>
         <v>9</v>
       </c>
@@ -2748,7 +2759,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -2760,35 +2771,35 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
@@ -2827,17 +2838,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -2849,15 +2860,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>18500</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2865,21 +2876,21 @@
           <t>as advised at last renewal</t>
         </is>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="20">
         <f>ROW()</f>
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>14400</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>0.75</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2887,21 +2898,21 @@
           <t>booked to 30.09</t>
         </is>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="20">
         <f>ROW()</f>
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>19200</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2909,21 +2920,21 @@
           <t>current view</t>
         </is>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>20900</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2931,18 +2942,18 @@
           <t>renewal projection</t>
         </is>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>2024 actual</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>17800</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2957,14 +2968,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3002,7 +3013,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -3014,49 +3025,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Transpose_1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Header_1 = C</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Info_1 = 14</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
@@ -3066,39 +3077,39 @@
           <t>Period</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>2024 actual</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
@@ -3108,24 +3119,24 @@
           <t>Share %</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="23" t="n">
         <v>0.75</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="22" t="n">
+      <c r="H9" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3135,24 +3146,24 @@
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>18500</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>14400</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>19200</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="17" t="n">
         <v>20900</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="17" t="n">
         <v>17800</v>
       </c>
     </row>
@@ -3194,19 +3205,19 @@
           <t>selector →</t>
         </is>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <f>COLUMN()</f>
         <v>4</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <f>COLUMN()</f>
         <v>5</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="20">
         <f>COLUMN()</f>
         <v>6</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="20">
         <f>COLUMN()</f>
         <v>7</v>
       </c>
@@ -3243,7 +3254,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -3255,49 +3266,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Threshold = 500</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
@@ -3336,27 +3347,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Name of Loss</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Date of Loss</t>
         </is>
@@ -3373,7 +3384,7 @@
           <t>CL-2100</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -3383,13 +3394,13 @@
           <t>Warehouse fire, Lyon</t>
         </is>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>1850</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="24" t="n">
         <v>44269</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
@@ -3400,7 +3411,7 @@
           <t>CL-2101</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -3410,13 +3421,13 @@
           <t>Machinery breakdown, Hamburg</t>
         </is>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>920</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="24" t="n">
         <v>44441</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -3427,7 +3438,7 @@
           <t>CL-2102</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3437,13 +3448,13 @@
           <t>Factory fire, Rotterdam</t>
         </is>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>3400</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="24" t="n">
         <v>44953</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -3454,7 +3465,7 @@
           <t>CL-2103</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3464,13 +3475,13 @@
           <t>Explosion, Antwerp</t>
         </is>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="24" t="n">
         <v>45092</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -3481,7 +3492,7 @@
           <t>CL-2104</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3491,13 +3502,13 @@
           <t>Storm damage, Bremen</t>
         </is>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>780</v>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="F15" s="24" t="n">
         <v>45238</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -3508,7 +3519,7 @@
           <t>CL-2105</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -3518,13 +3529,13 @@
           <t>Chemical plant fire, Basel</t>
         </is>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>2600</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="24" t="n">
         <v>45431</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
@@ -3535,7 +3546,7 @@
           <t>CL-2106</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -3545,13 +3556,13 @@
           <t>Cold store collapse, Milan</t>
         </is>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>1420</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="24" t="n">
         <v>45699</v>
       </c>
-      <c r="J17" s="19">
+      <c r="J17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
@@ -3562,7 +3573,7 @@
           <t>CL-2107</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -3572,13 +3583,13 @@
           <t>Transformer fire, Porto</t>
         </is>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>640</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="24" t="n">
         <v>45892</v>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="20">
         <f>ROW()</f>
         <v>18</v>
       </c>
@@ -3589,7 +3600,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="22">
         <f>SUM(E11:E18)</f>
         <v>12760</v>
       </c>
@@ -3600,14 +3611,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V94"/>
+  <dimension ref="B1:V96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2028,29 +2028,53 @@
     <row r="91">
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="8" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V96"/>
+  <dimension ref="B1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Greyed rows are provisional sketches, not yet specified. 04 is specified, though this Fire-only pack carries no cat sheet.</t>
+          <t>Greyed rows are declared but not yet implemented end to end. 04 is implemented, though this Fire-only pack carries no cat sheet.</t>
         </is>
       </c>
     </row>
@@ -904,35 +904,50 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Sum Insured</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Premium</t>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="P9" s="7" t="inlineStr">
+      <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>Exposure basis</t>
         </is>
       </c>
-      <c r="Q9" s="7" t="inlineStr">
+      <c r="R9" s="7" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1291,7 +1306,7 @@
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured</t>
+          <t>Band from</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -1303,31 +1318,31 @@
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Band to</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
+          <t>Claim Reference</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1339,7 +1354,7 @@
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1351,408 +1366,352 @@
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Name of Loss</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Number of Claims</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Number of Claims</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook. Year is text because 2026 and '2026 9 months' are two records.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="3" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="8" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Paid | Incurred</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="3" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="8" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>9 months</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="2" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically: est comes before 9 months even though '9' &lt; 'e'. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="3" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t>01 History.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C75" s="12" t="inlineStr">
-        <is>
-          <t>01 History.Premium@{N}</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E75" s="12" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>02 EPI.EPI@{N} re-est</t>
+          <t>01 History.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
@@ -1761,7 +1720,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
@@ -1775,29 +1734,29 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>SUM(03 Large.Loss amount@{Y})</t>
+          <t>01 History.Premium@{N}</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>01 History.Incurred Losses@{Y}</t>
+          <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
@@ -1810,34 +1769,34 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>01 History.Year basis</t>
+          <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>03 Large.Year basis</t>
+          <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
@@ -1850,24 +1809,24 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SUM(04 Cat.Loss amount@{Y})</t>
+          <t>SUM(03 Large.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -1890,19 +1849,19 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>per risk</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-09</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -1917,7 +1876,7 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>04 Cat.Year basis</t>
+          <t>03 Large.Year basis</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
@@ -1930,151 +1889,231 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04 Cat.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Year basis</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>04 Cat.Year basis</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="2" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="3" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="8" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;col&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;row&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Transpose_i</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="8" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V98"/>
+  <dimension ref="B1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -904,12 +904,12 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Band from</t>
+          <t>Band from (optional)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Band to</t>
+          <t>Band to (optional)</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -944,10 +944,25 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
           <t>Exposure basis</t>
         </is>
       </c>
-      <c r="R9" s="7" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>Layered business</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1536,262 +1551,206 @@
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Includes fac</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>yes | no</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Layered business</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>included | excluded</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="3" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="8" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>9 months</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically: est comes before 9 months even though '9' &lt; 'e'. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="3" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>01 History.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>01 History.Premium@{N}</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>02 EPI.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>02 EPI.EPI@{N} re-est</t>
+          <t>01 History.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -1800,7 +1759,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -1814,29 +1773,29 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SUM(03 Large.Loss amount@{Y})</t>
+          <t>01 History.Premium@{N}</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>01 History.Incurred Losses@{Y}</t>
+          <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
@@ -1849,34 +1808,34 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>01 History.Year basis</t>
+          <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>03 Large.Year basis</t>
+          <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
@@ -1889,24 +1848,24 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>SUM(04 Cat.Loss amount@{Y})</t>
+          <t>SUM(03 Large.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -1929,19 +1888,19 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>per risk</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-09</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -1956,7 +1915,7 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>04 Cat.Year basis</t>
+          <t>03 Large.Year basis</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
@@ -1969,151 +1928,231 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04 Cat.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Year basis</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>04 Cat.Year basis</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="2" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="3" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="8" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;col&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;row&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Transpose_i</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="8" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -13,6 +13,7 @@
     <sheet name="02. EPI Projections" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="02. EPI Projections_Transposed" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="03. Large Losses" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="05. Risk Profiles" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,12 +55,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00999999"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Consolas"/>
       <sz val="9"/>
     </font>
@@ -72,6 +67,12 @@
     <font>
       <name val="Arial"/>
       <color rgb="007F6000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00999999"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -137,15 +138,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -887,82 +888,82 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>05. Risk Profiles</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>05 Profile</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Band from (optional)</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Band to (optional)</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="P9" s="7" t="inlineStr">
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="Q9" s="7" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="R9" s="7" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>Exposure basis</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="6" t="inlineStr">
         <is>
           <t>Includes fac</t>
         </is>
       </c>
-      <c r="T9" s="7" t="inlineStr">
+      <c r="T9" s="6" t="inlineStr">
         <is>
           <t>Layered business</t>
         </is>
       </c>
-      <c r="U9" s="7" t="inlineStr">
+      <c r="U9" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1105,17 +1106,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Datasets</t>
         </is>
@@ -1134,7 +1135,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 03</t>
+          <t>01, 02, 03, 05</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1154,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -1170,7 +1171,7 @@
           <t>Actual year</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="8" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1216,7 +1217,7 @@
           <t>Loss share warning</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="9" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1235,12 +1236,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
@@ -1477,12 +1478,12 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Permitted values</t>
         </is>
@@ -1640,19 +1641,19 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="11" t="n">
+      <c r="B70" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -1662,7 +1663,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="11" t="n">
+      <c r="B71" s="10" t="n">
         <v>2</v>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -1672,7 +1673,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="11" t="n">
+      <c r="B72" s="10" t="n">
         <v>3</v>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -1696,64 +1697,64 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="I77" s="8" t="inlineStr">
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C78" s="11" t="inlineStr">
         <is>
           <t>01 History.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E78" s="12" t="inlineStr">
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} 9 months</t>
         </is>
@@ -1778,22 +1779,22 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C79" s="12" t="inlineStr">
+      <c r="C79" s="11" t="inlineStr">
         <is>
           <t>01 History.Premium@{N}</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="E79" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
@@ -1818,22 +1819,22 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="E80" s="12" t="inlineStr">
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} 9 months</t>
         </is>
@@ -1858,22 +1859,22 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="C81" s="12" t="inlineStr">
+      <c r="C81" s="11" t="inlineStr">
         <is>
           <t>SUM(03 Large.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="E81" s="11" t="inlineStr">
         <is>
           <t>01 History.Incurred Losses@{Y}</t>
         </is>
@@ -1898,22 +1899,22 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>R-09</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>01 History.Year basis</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>03 Large.Year basis</t>
         </is>
@@ -1938,22 +1939,22 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
       </c>
-      <c r="C83" s="12" t="inlineStr">
+      <c r="C83" s="11" t="inlineStr">
         <is>
           <t>SUM(04 Cat.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="E83" s="11" t="inlineStr">
         <is>
           <t>01 History.Incurred Losses@{Y}</t>
         </is>
@@ -1978,22 +1979,22 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>01 History.Year basis</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E84" s="11" t="inlineStr">
         <is>
           <t>04 Cat.Year basis</t>
         </is>
@@ -2032,19 +2033,19 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="13" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
@@ -2056,7 +2057,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="13" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
@@ -2068,7 +2069,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="13" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
@@ -2080,7 +2081,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="13" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
@@ -2092,7 +2093,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="13" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
@@ -2104,7 +2105,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="13" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>Dataset_i = &lt;key&gt;</t>
         </is>
@@ -2116,7 +2117,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="13" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>Section_i = &lt;name&gt;</t>
         </is>
@@ -2128,7 +2129,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="13" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
@@ -2140,7 +2141,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="13" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
@@ -2152,7 +2153,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2184,7 +2185,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -2196,77 +2197,77 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Treaty XYZ — Property per Risk XL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>UW Year</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Comm. %</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2310,7 +2311,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="10" t="n">
         <v>2021</v>
       </c>
       <c r="C9" s="17" t="n">
@@ -2334,7 +2335,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="10" t="n">
         <v>2022</v>
       </c>
       <c r="C10" s="17" t="n">
@@ -2358,7 +2359,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="10" t="n">
         <v>2023</v>
       </c>
       <c r="C11" s="17" t="n">
@@ -2382,7 +2383,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="10" t="n">
         <v>2024</v>
       </c>
       <c r="C12" s="17" t="n">
@@ -2406,7 +2407,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="10" t="n">
         <v>2025</v>
       </c>
       <c r="C13" s="17" t="n">
@@ -2456,12 +2457,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -2492,7 +2493,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2530,7 +2531,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -2542,21 +2543,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
@@ -2584,12 +2585,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>UW Year</t>
         </is>
@@ -2599,19 +2600,19 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="10" t="n">
         <v>2021</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="10" t="n">
         <v>2022</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="10" t="n">
         <v>2023</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="10" t="n">
         <v>2024</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="10" t="n">
         <v>2025</v>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -2619,19 +2620,19 @@
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
@@ -2660,12 +2661,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
@@ -2699,7 +2700,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Comm. %</t>
         </is>
@@ -2724,7 +2725,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
@@ -2749,12 +2750,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2788,7 +2789,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2861,7 +2862,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -2873,57 +2874,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -3077,7 +3078,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3115,7 +3116,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -3127,21 +3128,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -3169,12 +3170,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
@@ -3211,12 +3212,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -3238,12 +3239,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
@@ -3270,7 +3271,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -3356,7 +3357,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -3368,76 +3369,76 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Threshold = 500</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Claim no.</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Occurred</t>
         </is>
@@ -3697,7 +3698,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3720,7 +3721,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3730,6 +3731,341 @@
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>2022 has no large loss. The annual table in step 2 shows it as 0, because an absent year reads as 'no data' rather than 'nothing happened'.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>05. Risk Profiles — Fire, as at 30.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Section = Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Currency = USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Scale = 1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Exposure basis = Sum Insured</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Includes fac = yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Layered business = excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Sum insured</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: the bounds are declared, so nothing is read off the label</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>0 - 1 000</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>620</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>310000</v>
+      </c>
+      <c r="J11" s="20">
+        <f>ROW()</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1 001 - 5 000</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="J12" s="20">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>5 001 - 10 000</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>5001</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="J13" s="20">
+        <f>ROW()</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>10 001 - 25 000</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>10001</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>2010000</v>
+      </c>
+      <c r="J14" s="20">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 25 000</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="J15" s="20">
+        <f>ROW()</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E16" s="22">
+        <f>SUM(E11:E15)</f>
+        <v>20150</v>
+      </c>
+      <c r="F16" s="22">
+        <f>SUM(F11:F15)</f>
+        <v>1505</v>
+      </c>
+      <c r="G16" s="22">
+        <f>SUM(G11:G15)</f>
+        <v>6630000</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Info_1 = J</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>The top band is open at the top: its upper bound is absent, not zero. Bands are grouped with spaces, which is unambiguous; a comma-grouped label would be refused by the decimal rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>As at = 30.09.2025</t>
         </is>
       </c>
     </row>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Band (optional)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +139,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -521,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V100"/>
+  <dimension ref="B1:V117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1101,1059 +1102,1359 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>⟦SECTIONS⟧</t>
+          <t>⟦INVENTORY⟧</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Datasets</t>
+          <t>Holds</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>State</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Fire</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>History</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 03, 05</t>
+          <t>Premium and loss history per section</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>EPI Projections</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Estimated premium income, N and N+1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>One per-risk section: a Fire treaty. Large losses (03) apply; cat losses (04) do not, so rules scoped 'cat' are not applicable.</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Large Losses</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Individual large claims, per-risk sections</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Cat Losses</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Catastrophe events, cat sections</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>⟦GLOBAL⟧</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Risk Profiles</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Banded exposure — the per-risk rating basis</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>EQ Aggs</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Earthquake sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Actual year</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>2025</v>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Wind Aggs</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Treaty type</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Fire</t>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Splits</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Occupancy x cover (Fire) or x Projects/Renewables (Eng.)</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>axes settled, measures open</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cedent</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Example Insurance SA</t>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Rate Development</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Rate change history — optional</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Treaty</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Property per Risk XL</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Triangles</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Loss development triangles</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Loss share warning</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Actual year is N: the expiring year. The renewal being underwritten is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>⟦TYPES⟧</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Exchange rates</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FX rates for conversion between currencies</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Collected step-2 blocks — written, never read</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Every dataset the tool knows, whether or not this pack carries it. The register above lists what is here; ⟦SECTIONS⟧ says which roles each section expects, so a missing sheet reads as structure rather than as a gap.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Type</t>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>⟦SECTIONS⟧</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Datasets</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Premium</t>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Incurred Losses</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 03, 05</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Band</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>One per-risk section: a Fire treaty. Large losses (03) apply; cat losses (04) do not, so rules scoped 'cat' are not applicable.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Number of Risks</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>⟦GLOBAL⟧</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Band from</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Band to</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
+          <t>Actual year</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+          <t>Treaty type</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Example Insurance SA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+          <t>Treaty</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Property per Risk XL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Event ID</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
+          <t>Loss share warning</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Loss amount</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Number of Claims</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Actual year is N: the expiring year. The renewal being underwritten is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Date of Loss</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>date</t>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Event Date</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>date</t>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Event End Date</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>A field name carries one type across the whole workbook. Year is text because 2026 and '2026 9 months' are two records.</t>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Incurred Losses</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>EPI</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>⟦VOCABULARY⟧</t>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Permitted values</t>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>Claim Reference</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Includes fac</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>yes | no</t>
+          <t>Name of Loss</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Layered business</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>included | excluded</t>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Loss amount</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>100% | ceded only</t>
+          <t>Number of Claims</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Event Date | Event End Date</t>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>A field name carries one type across the whole workbook. Year is text because 2026 and '2026 9 months' are two records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>⟦VOCABULARY⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Permitted values</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Year basis</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>UW | Occurrence</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Premium basis</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Loss basis</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Paid | Incurred</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>PF transfer</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>with clean cut | without clean cut | none</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured | EML | PML | MPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>yes | no</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Layered business</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>included | excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="3" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="7" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="10" t="n">
+    <row r="87">
+      <c r="B87" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="10" t="n">
+    <row r="88">
+      <c r="B88" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="10" t="n">
+    <row r="89">
+      <c r="B89" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="2" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically: est comes before 9 months even though '9' &lt; 'e'. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="3" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="7" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="7" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C78" s="11" t="inlineStr">
+      <c r="C95" s="12" t="inlineStr">
         <is>
           <t>01 History.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E78" s="11" t="inlineStr">
+      <c r="E95" s="12" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F95" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="7" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C79" s="11" t="inlineStr">
+      <c r="C96" s="12" t="inlineStr">
         <is>
           <t>01 History.Premium@{N}</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E79" s="11" t="inlineStr">
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F96" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G96" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H96" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="7" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="C80" s="11" t="inlineStr">
+      <c r="C97" s="12" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="E80" s="11" t="inlineStr">
+      <c r="E97" s="12" t="inlineStr">
         <is>
           <t>02 EPI.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H97" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="7" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="C81" s="11" t="inlineStr">
+      <c r="C98" s="12" t="inlineStr">
         <is>
           <t>SUM(03 Large.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E81" s="11" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>01 History.Incurred Losses@{Y}</t>
         </is>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H98" s="5" t="inlineStr">
         <is>
           <t>per risk</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="7" t="inlineStr">
+    <row r="99">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>R-09</t>
         </is>
       </c>
-      <c r="C82" s="11" t="inlineStr">
+      <c r="C99" s="12" t="inlineStr">
         <is>
           <t>01 History.Year basis</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr">
+      <c r="E99" s="12" t="inlineStr">
         <is>
           <t>03 Large.Year basis</t>
         </is>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F99" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G99" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>per risk</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>history and large losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>R-02</t>
-        </is>
-      </c>
-      <c r="C83" s="11" t="inlineStr">
-        <is>
-          <t>SUM(04 Cat.Loss amount@{Y})</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Incurred Losses@{Y}</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>R-10</t>
-        </is>
-      </c>
-      <c r="C84" s="11" t="inlineStr">
-        <is>
-          <t>01 History.Year basis</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>04 Cat.Year basis</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>history and cat losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>Marker</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;row&gt;</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>Transpose_i</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>block i is transposed</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t>Dataset_i = &lt;key&gt;</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>Section_i = &lt;name&gt;</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>which section of the treaty block i belongs to</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04 Cat.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>01 History.Year basis</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>04 Cat.Year basis</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>history and cat losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Forms: &lt;key&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands the rule once per year. A rule is skipped, not guessed, when a basis or currency differs; it is 'not applicable' when the dataset is absent from this pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Marker</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>Header_i</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>Header_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this column is block i's extraction column</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;row&gt;</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>Transpose_i</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>block i is transposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>Dataset_i = &lt;key&gt;</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>the same, declared as a hypothesis — raises a query</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2185,7 +2486,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -2197,7 +2498,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
@@ -2209,65 +2510,65 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>UW Year</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Comm. %</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2284,22 +2585,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2311,153 +2612,153 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>1240</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>15900</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.225</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>1.02</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <v>14930</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="21">
         <f>ROW()</f>
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>1310</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>16740</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.225</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="20" t="n">
         <v>1.04</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>10030</v>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="21">
         <f>ROW()</f>
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>1395</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>17520</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>0.23</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>1.06</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <v>12660</v>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="21">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>1460</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>18390</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>0.23</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <v>1.03</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>11700</v>
       </c>
-      <c r="L12" s="20">
+      <c r="L12" s="21">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>1505</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>19200</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>0.235</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="20" t="n">
         <v>1.05</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>10250</v>
       </c>
-      <c r="L13" s="20">
+      <c r="L13" s="21">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>1180</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>14400</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>0.235</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="20" t="n">
         <v>1.05</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>7100</v>
       </c>
-      <c r="L14" s="20">
+      <c r="L14" s="21">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -2467,15 +2768,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="23">
         <f>SUM(C9:C14)</f>
         <v>8090</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="23">
         <f>SUM(D9:D14)</f>
         <v>102150</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="23">
         <f>SUM(G9:G14)</f>
         <v>66670</v>
       </c>
@@ -2486,14 +2787,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2531,7 +2832,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -2543,79 +2844,79 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Transpose_1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Header_1 = C</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Info_1 = 16</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>UW Year</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
@@ -2627,169 +2928,169 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>1240</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>1310</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>1395</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <v>1460</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <v>1505</v>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="18" t="n">
         <v>1180</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="23">
         <f>SUM(D9:I9)</f>
         <v>8090</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>15900</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>16740</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>17520</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>18390</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <v>19200</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <v>14400</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="23">
         <f>SUM(D10:I10)</f>
         <v>102150</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Comm. %</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>0.225</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>0.225</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.23</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.23</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="19" t="n">
         <v>0.235</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="19" t="n">
         <v>0.235</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="20" t="n">
         <v>1.02</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="20" t="n">
         <v>1.04</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <v>1.06</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="20" t="n">
         <v>1.03</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="20" t="n">
         <v>1.05</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="20" t="n">
         <v>1.05</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>14930</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>10030</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>12660</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>11700</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="18" t="n">
         <v>10250</v>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="18" t="n">
         <v>7100</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="23">
         <f>SUM(D13:I13)</f>
         <v>66670</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2799,27 +3100,27 @@
           <t>selector →</t>
         </is>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <f>COLUMN()</f>
         <v>4</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>COLUMN()</f>
         <v>5</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <f>COLUMN()</f>
         <v>6</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="21">
         <f>COLUMN()</f>
         <v>7</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="21">
         <f>COLUMN()</f>
         <v>8</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="21">
         <f>COLUMN()</f>
         <v>9</v>
       </c>
@@ -2862,7 +3163,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -2874,57 +3175,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -2941,17 +3242,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -2963,15 +3264,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>18500</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2979,21 +3280,21 @@
           <t>as advised at last renewal</t>
         </is>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="21">
         <f>ROW()</f>
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>14400</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="24" t="n">
         <v>0.75</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3001,21 +3302,21 @@
           <t>booked to 30.09</t>
         </is>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="21">
         <f>ROW()</f>
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>19200</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3023,21 +3324,21 @@
           <t>current view</t>
         </is>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="21">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>20900</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3045,18 +3346,18 @@
           <t>renewal projection</t>
         </is>
       </c>
-      <c r="K12" s="20">
+      <c r="K12" s="21">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>2024 actual</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>17800</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3071,14 +3372,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3116,7 +3417,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -3128,150 +3429,150 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Transpose_1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Header_1 = C</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Info_1 = 14</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>2024 actual</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="24" t="n">
         <v>0.75</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="23" t="n">
+      <c r="H9" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>18500</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>14400</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>19200</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>20900</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <v>17800</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -3308,19 +3609,19 @@
           <t>selector →</t>
         </is>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <f>COLUMN()</f>
         <v>4</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <f>COLUMN()</f>
         <v>5</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <f>COLUMN()</f>
         <v>6</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <f>COLUMN()</f>
         <v>7</v>
       </c>
@@ -3357,7 +3658,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
@@ -3369,76 +3670,76 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Threshold = 500</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Claim no.</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Occurred</t>
         </is>
@@ -3450,27 +3751,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Name of Loss</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Date of Loss</t>
         </is>
@@ -3487,7 +3788,7 @@
           <t>CL-2100</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -3497,13 +3798,13 @@
           <t>Warehouse fire, Lyon</t>
         </is>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>1850</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="25" t="n">
         <v>44269</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="21">
         <f>ROW()</f>
         <v>11</v>
       </c>
@@ -3514,7 +3815,7 @@
           <t>CL-2101</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -3524,13 +3825,13 @@
           <t>Machinery breakdown, Hamburg</t>
         </is>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>920</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="25" t="n">
         <v>44441</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="21">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -3541,7 +3842,7 @@
           <t>CL-2102</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3551,13 +3852,13 @@
           <t>Factory fire, Rotterdam</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>3400</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <v>44953</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="21">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -3568,7 +3869,7 @@
           <t>CL-2103</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3578,13 +3879,13 @@
           <t>Explosion, Antwerp</t>
         </is>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>1150</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="25" t="n">
         <v>45092</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="21">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -3595,7 +3896,7 @@
           <t>CL-2104</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3605,13 +3906,13 @@
           <t>Storm damage, Bremen</t>
         </is>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>780</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="25" t="n">
         <v>45238</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="21">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -3622,7 +3923,7 @@
           <t>CL-2105</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -3632,13 +3933,13 @@
           <t>Chemical plant fire, Basel</t>
         </is>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>2600</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="25" t="n">
         <v>45431</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="21">
         <f>ROW()</f>
         <v>16</v>
       </c>
@@ -3649,7 +3950,7 @@
           <t>CL-2106</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -3659,13 +3960,13 @@
           <t>Cold store collapse, Milan</t>
         </is>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <v>1420</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="25" t="n">
         <v>45699</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="21">
         <f>ROW()</f>
         <v>17</v>
       </c>
@@ -3676,7 +3977,7 @@
           <t>CL-2107</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -3686,13 +3987,13 @@
           <t>Transformer fire, Porto</t>
         </is>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <v>640</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="25" t="n">
         <v>45892</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="21">
         <f>ROW()</f>
         <v>18</v>
       </c>
@@ -3703,7 +4004,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="23">
         <f>SUM(E11:E18)</f>
         <v>12760</v>
       </c>
@@ -3714,14 +4015,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3767,81 +4068,81 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Exposure basis = Sum Insured</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Includes fac = yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Layered business = excluded</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>Sum insured</t>
         </is>
@@ -3853,37 +4154,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Band from</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Band to</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
@@ -3900,22 +4201,22 @@
           <t>0 - 1 000</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>1000</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>2150</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>620</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <v>310000</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="21">
         <f>ROW()</f>
         <v>11</v>
       </c>
@@ -3926,22 +4227,22 @@
           <t>1 001 - 5 000</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>1001</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>4900</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>480</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>1290000</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="21">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -3952,22 +4253,22 @@
           <t>5 001 - 10 000</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>5001</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>5300</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>260</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>1880000</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="21">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -3978,22 +4279,22 @@
           <t>10 001 - 25 000</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>10001</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>25000</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>4700</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <v>118</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>2010000</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="21">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -4004,24 +4305,24 @@
           <t>&gt; 25 000</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>25000</v>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>3100</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="18" t="n">
         <v>27</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <v>1140000</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="21">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -4032,15 +4333,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="23">
         <f>SUM(E11:E15)</f>
         <v>20150</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="23">
         <f>SUM(F11:F15)</f>
         <v>1505</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <f>SUM(G11:G15)</f>
         <v>6630000</v>
       </c>
@@ -4051,7 +4352,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
@@ -4063,7 +4364,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>As at = 30.09.2025</t>
         </is>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -1295,12 +1295,12 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Occupancy x cover (Fire) or x Projects/Renewables (Eng.)</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>axes settled, measures open</t>
+          <t>The cedent's book split — sums insured, one block per section</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>

--- a/Intake_v1.xlsx
+++ b/Intake_v1.xlsx
@@ -1317,12 +1317,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Rate change history — optional</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>outstanding</t>
+          <t>The rate change a submission claims — the UW's own sheet</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
